--- a/src/Planning_engine/ALICE_BIM_mapper/inputs/ALICE_macro.xlsx
+++ b/src/Planning_engine/ALICE_BIM_mapper/inputs/ALICE_macro.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="366">
   <si>
     <t xml:space="preserve">Alice WBS Id*</t>
   </si>
@@ -236,568 +236,625 @@
     <t xml:space="preserve">Capacity</t>
   </si>
   <si>
+    <t>Backfill/Compaction (cy/hr)</t>
+  </si>
+  <si>
+    <t>backfill_compaction_cy_hr_</t>
+  </si>
+  <si>
+    <t>MEP Rough-In per Trade (sf/hr)</t>
+  </si>
+  <si>
+    <t>mep_rough_in_per_trade_sf_hr_</t>
+  </si>
+  <si>
+    <t>Hauling (cy/hr)</t>
+  </si>
+  <si>
+    <t>hauling_cy_hr_</t>
+  </si>
+  <si>
+    <t>Interior (sf/hr)</t>
+  </si>
+  <si>
+    <t>interior_sf_hr_</t>
+  </si>
+  <si>
+    <t>Excavation (cy/hr)</t>
+  </si>
+  <si>
+    <t>excavation_cy_hr_</t>
+  </si>
+  <si>
+    <t>Proofroll (sf/hr)</t>
+  </si>
+  <si>
+    <t>proofroll_sf_hr_</t>
+  </si>
+  <si>
+    <t>Slab-on-Grade (sf/hr)</t>
+  </si>
+  <si>
+    <t>slab_on_grade_sf_hr_</t>
+  </si>
+  <si>
+    <t>A1070</t>
+  </si>
+  <si>
+    <t>Site Setup Crew</t>
+  </si>
+  <si>
+    <t>A1080</t>
+  </si>
+  <si>
+    <t>A1090</t>
+  </si>
+  <si>
+    <t>A1100</t>
+  </si>
+  <si>
+    <t>A1110</t>
+  </si>
+  <si>
+    <t>Tree Removal / Clearing Crew</t>
+  </si>
+  <si>
+    <t>A1120</t>
+  </si>
+  <si>
+    <t>Demolition Crew (bleachers)</t>
+  </si>
+  <si>
+    <t>A1140</t>
+  </si>
+  <si>
+    <t>A1150</t>
+  </si>
+  <si>
     <t>A1170</t>
   </si>
   <si>
+    <t>Earthwork Crew (excavation)</t>
+  </si>
+  <si>
+    <t>A1180</t>
+  </si>
+  <si>
+    <t>Shoring / Stabilization Crew</t>
+  </si>
+  <si>
+    <t>A1190</t>
+  </si>
+  <si>
+    <t>A1200</t>
+  </si>
+  <si>
+    <t>Concrete Crew</t>
+  </si>
+  <si>
+    <t>A1210</t>
+  </si>
+  <si>
+    <t>A1220</t>
+  </si>
+  <si>
+    <t>A1230</t>
+  </si>
+  <si>
+    <t>A1240</t>
+  </si>
+  <si>
+    <t>A1250</t>
+  </si>
+  <si>
+    <t>Underground Utilities Crew</t>
+  </si>
+  <si>
+    <t>A1260</t>
+  </si>
+  <si>
+    <t>Exc</t>
+  </si>
+  <si>
+    <t>A1270</t>
+  </si>
+  <si>
+    <t>A1330</t>
+  </si>
+  <si>
+    <t>Structural Crew</t>
+  </si>
+  <si>
+    <t>A1340</t>
+  </si>
+  <si>
+    <t>A1420</t>
+  </si>
+  <si>
+    <t>A1590</t>
+  </si>
+  <si>
+    <t>Facade Install Crew</t>
+  </si>
+  <si>
+    <t>A1610</t>
+  </si>
+  <si>
+    <t>A1670</t>
+  </si>
+  <si>
+    <t>HVAC Rough-In Crew</t>
+  </si>
+  <si>
+    <t>A1680</t>
+  </si>
+  <si>
+    <t>Electrical Rough-In Crew</t>
+  </si>
+  <si>
+    <t>A1690</t>
+  </si>
+  <si>
+    <t>Plumbing + Fire Protection Rough-In Crew</t>
+  </si>
+  <si>
+    <t>A1740</t>
+  </si>
+  <si>
+    <t>Interiors Crew</t>
+  </si>
+  <si>
+    <t>A1760</t>
+  </si>
+  <si>
+    <t>A1820</t>
+  </si>
+  <si>
+    <t>Commissioning / Controls Support</t>
+  </si>
+  <si>
+    <t>A1830</t>
+  </si>
+  <si>
+    <t>TAB Team</t>
+  </si>
+  <si>
+    <t>A1840</t>
+  </si>
+  <si>
+    <t>A1860</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>total_cost</t>
+  </si>
+  <si>
+    <t>CONSUMABLE</t>
+  </si>
+  <si>
+    <t>3837e7c2-0906-4333-ac9b-a2737d9ef3ab</t>
+  </si>
+  <si>
+    <t>Island 2026</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>cbd410b2-5548-4cd2-8527-f2345a50d57f</t>
+  </si>
+  <si>
+    <t>SITE PREPARATION &amp; DEMOLITION</t>
+  </si>
+  <si>
+    <t>project.SITE PREPARATION &amp; DEMOLITION</t>
+  </si>
+  <si>
+    <t>0d25cbc5-489e-404b-bca9-c37d58b2aab2</t>
+  </si>
+  <si>
+    <t>EARTHWORK &amp; BASEMENT</t>
+  </si>
+  <si>
+    <t>project.EARTHWORK &amp; BASEMENT</t>
+  </si>
+  <si>
+    <t>877325b6-0ec2-4dc8-b9e3-cfa6b8292d16</t>
+  </si>
+  <si>
+    <t>SUPERSTRUCTURE</t>
+  </si>
+  <si>
+    <t>project.SUPERSTRUCTURE – ZONE A</t>
+  </si>
+  <si>
+    <t>63195f08-e779-4f3a-ae3a-306d40e10c1c</t>
+  </si>
+  <si>
+    <t>ENVELOPE</t>
+  </si>
+  <si>
+    <t>project.ENVELOPE</t>
+  </si>
+  <si>
+    <t>c3929e98-3e87-4181-a90c-ec2646e7d440</t>
+  </si>
+  <si>
+    <t>MEP INSTALLATION</t>
+  </si>
+  <si>
+    <t>project.MEP INSTALLATION</t>
+  </si>
+  <si>
+    <t>da7c403f-4319-48fd-8009-37270386cab6</t>
+  </si>
+  <si>
+    <t>INTERIOR</t>
+  </si>
+  <si>
+    <t>project.INTERIOR FINISHES</t>
+  </si>
+  <si>
+    <t>383f728a-1104-4558-be7b-db47650d4deb</t>
+  </si>
+  <si>
+    <t>COMMISSIONING &amp; CLOSEOUT</t>
+  </si>
+  <si>
+    <t>project.COMMISSIONING &amp; CLOSEOUT</t>
+  </si>
+  <si>
+    <t>Install Construction Fencing</t>
+  </si>
+  <si>
+    <t>REGULAR</t>
+  </si>
+  <si>
+    <t>MANUAL</t>
+  </si>
+  <si>
+    <t>Default calendar</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>NOT_STARTED</t>
+  </si>
+  <si>
+    <t>2029-10-01T09:00</t>
+  </si>
+  <si>
+    <t>2029-10-03T17:00</t>
+  </si>
+  <si>
+    <t>Install Site Office &amp; Welfare Units</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>2029-10-04T09:00</t>
+  </si>
+  <si>
+    <t>2029-10-09T17:00</t>
+  </si>
+  <si>
+    <t>Temporary Water Installation</t>
+  </si>
+  <si>
+    <t>2029-10-08T17:00</t>
+  </si>
+  <si>
+    <t>Temporary Power Installation</t>
+  </si>
+  <si>
+    <t>Tree Removal &amp; Clearing</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>2029-10-10T17:00</t>
+  </si>
+  <si>
+    <t>Bleacher Demolition</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>2029-10-12T17:00</t>
+  </si>
+  <si>
+    <t>Crane Pad Construction</t>
+  </si>
+  <si>
+    <t>2029-10-11T09:00</t>
+  </si>
+  <si>
+    <t>2029-10-17T17:00</t>
+  </si>
+  <si>
+    <t>Laydown Area Preparation</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Full Basement Excavation</t>
+  </si>
+  <si>
+    <t>Shoring / Stabilization</t>
+  </si>
+  <si>
+    <t>2029-10-10T09:00</t>
+  </si>
+  <si>
+    <t>2029-10-16T17:00</t>
+  </si>
+  <si>
+    <t>Subgrade Preparation</t>
+  </si>
+  <si>
+    <t>2029-10-15T17:00</t>
+  </si>
+  <si>
+    <t>Footings – Form/Rebar/Pour</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>2029-10-16T09:00</t>
+  </si>
+  <si>
+    <t>2029-10-29T17:00</t>
+  </si>
+  <si>
+    <t>Grade Beams</t>
+  </si>
+  <si>
+    <t>2029-11-08T09:00</t>
+  </si>
+  <si>
+    <t>2029-11-16T17:00</t>
+  </si>
+  <si>
+    <t>Basement Retaining Walls</t>
+  </si>
+  <si>
+    <t>2029-11-19T09:00</t>
+  </si>
+  <si>
+    <t>2029-11-21T17:00</t>
+  </si>
+  <si>
+    <t>Waterproofing &amp; Drainage</t>
+  </si>
+  <si>
+    <t>2029-11-22T09:00</t>
+  </si>
+  <si>
+    <t>2029-11-28T17:00</t>
+  </si>
+  <si>
+    <t>Basement Slab on Grade</t>
+  </si>
+  <si>
+    <t>2029-12-17T09:00</t>
+  </si>
+  <si>
+    <t>2029-12-25T17:00</t>
+  </si>
+  <si>
+    <t>Underground Utilities</t>
+  </si>
+  <si>
+    <t>2029-11-29T09:00</t>
+  </si>
+  <si>
+    <t>2029-12-07T17:00</t>
+  </si>
+  <si>
+    <t>Backfill &amp; Compaction</t>
+  </si>
+  <si>
+    <t>2029-12-10T09:00</t>
+  </si>
+  <si>
+    <t>2029-12-14T17:00</t>
+  </si>
+  <si>
+    <t>Foundational Columns</t>
+  </si>
+  <si>
+    <t>2029-10-30T09:00</t>
+  </si>
+  <si>
+    <t>2029-11-07T17:00</t>
+  </si>
+  <si>
+    <t>Frame: Columns</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>2030-01-08T09:00</t>
+  </si>
+  <si>
+    <t>2030-01-15T17:00</t>
+  </si>
+  <si>
+    <t>Floor</t>
+  </si>
+  <si>
+    <t>2030-01-03T09:00</t>
+  </si>
+  <si>
+    <t>2030-01-07T17:00</t>
+  </si>
+  <si>
+    <t>A1350</t>
+  </si>
+  <si>
+    <t>Frame: Beams</t>
+  </si>
+  <si>
+    <t>2029-12-26T09:00</t>
+  </si>
+  <si>
+    <t>2030-01-02T17:00</t>
+  </si>
+  <si>
+    <t>Roof</t>
+  </si>
+  <si>
+    <t>2030-01-16T09:00</t>
+  </si>
+  <si>
+    <t>2030-01-21T17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass Install + Glazing </t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>2030-02-13T09:00</t>
+  </si>
+  <si>
+    <t>2030-03-06T17:00</t>
+  </si>
+  <si>
+    <t>A1600</t>
+  </si>
+  <si>
+    <t>Exterior Wall Install</t>
+  </si>
+  <si>
+    <t>2030-01-22T09:00</t>
+  </si>
+  <si>
+    <t>2030-02-12T17:00</t>
+  </si>
+  <si>
+    <t>Mesh Install</t>
+  </si>
+  <si>
+    <t>2030-03-07T09:00</t>
+  </si>
+  <si>
+    <t>2030-03-28T17:00</t>
+  </si>
+  <si>
+    <t>Mechanical Room Buildout</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>2030-03-26T17:00</t>
+  </si>
+  <si>
+    <t>Main Electrical &amp; Riser Install</t>
+  </si>
+  <si>
+    <t>MEP Rough-In</t>
+  </si>
+  <si>
+    <t>384</t>
+  </si>
+  <si>
+    <t>2030-03-27T09:00</t>
+  </si>
+  <si>
+    <t>2030-05-31T17:00</t>
+  </si>
+  <si>
+    <t>Interior Walls</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>2030-04-25T17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceiling Installation </t>
+  </si>
+  <si>
+    <t>2030-04-26T09:00</t>
+  </si>
+  <si>
+    <t>2030-05-17T17:00</t>
+  </si>
+  <si>
+    <t>MEP Start-Up</t>
+  </si>
+  <si>
+    <t>2030-05-20T09:00</t>
+  </si>
+  <si>
+    <t>2030-05-28T17:00</t>
+  </si>
+  <si>
+    <t>TAB</t>
+  </si>
+  <si>
+    <t>2030-05-29T09:00</t>
+  </si>
+  <si>
+    <t>2030-06-06T17:00</t>
+  </si>
+  <si>
+    <t>Integrated Systems Testing</t>
+  </si>
+  <si>
+    <t>2030-06-07T09:00</t>
+  </si>
+  <si>
+    <t>2030-06-13T17:00</t>
+  </si>
+  <si>
+    <t>Final Inspections</t>
+  </si>
+  <si>
+    <t>2030-05-24T17:00</t>
+  </si>
+  <si>
+    <t>A1880</t>
+  </si>
+  <si>
+    <t>Hurricane Contingency Buffer</t>
+  </si>
+  <si>
+    <t>2030-06-14T09:00</t>
+  </si>
+  <si>
+    <t>2030-07-03T17:00</t>
+  </si>
+  <si>
     <t>Excavator</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>A1190</t>
-  </si>
-  <si>
     <t>Compactor/Roller</t>
   </si>
   <si>
-    <t>A1200</t>
-  </si>
-  <si>
     <t>Concrete Pump</t>
   </si>
   <si>
-    <t>A1220</t>
-  </si>
-  <si>
-    <t>A1260</t>
-  </si>
-  <si>
-    <t>A1330</t>
-  </si>
-  <si>
     <t>Mobile Crane</t>
   </si>
   <si>
-    <t>A1340</t>
-  </si>
-  <si>
-    <t>A1420</t>
-  </si>
-  <si>
-    <t>A1590</t>
-  </si>
-  <si>
-    <t>A1070</t>
-  </si>
-  <si>
-    <t>Site Setup Crew</t>
-  </si>
-  <si>
-    <t>A1080</t>
-  </si>
-  <si>
-    <t>A1090</t>
-  </si>
-  <si>
-    <t>A1100</t>
-  </si>
-  <si>
-    <t>A1110</t>
-  </si>
-  <si>
-    <t>Tree Removal / Clearing Crew</t>
-  </si>
-  <si>
-    <t>A1120</t>
-  </si>
-  <si>
-    <t>Demolition Crew (bleachers)</t>
-  </si>
-  <si>
-    <t>A1140</t>
-  </si>
-  <si>
-    <t>A1150</t>
-  </si>
-  <si>
-    <t>Earthwork Crew (excavation)</t>
-  </si>
-  <si>
-    <t>A1180</t>
-  </si>
-  <si>
-    <t>Shoring / Stabilization Crew</t>
-  </si>
-  <si>
-    <t>Concrete Crew</t>
-  </si>
-  <si>
-    <t>A1210</t>
-  </si>
-  <si>
-    <t>A1230</t>
-  </si>
-  <si>
-    <t>A1240</t>
-  </si>
-  <si>
-    <t>A1250</t>
-  </si>
-  <si>
-    <t>Underground Utilities Crew</t>
-  </si>
-  <si>
-    <t>Exc</t>
-  </si>
-  <si>
-    <t>A1270</t>
-  </si>
-  <si>
-    <t>Structural Crew</t>
-  </si>
-  <si>
-    <t>Facade Install Crew</t>
-  </si>
-  <si>
-    <t>A1670</t>
-  </si>
-  <si>
-    <t>HVAC Rough-In Crew</t>
-  </si>
-  <si>
-    <t>A1680</t>
-  </si>
-  <si>
-    <t>Electrical Rough-In Crew</t>
-  </si>
-  <si>
-    <t>A1690</t>
-  </si>
-  <si>
-    <t>Plumbing + Fire Protection Rough-In Crew</t>
-  </si>
-  <si>
-    <t>A1740</t>
-  </si>
-  <si>
-    <t>Interiors Crew</t>
-  </si>
-  <si>
-    <t>A1750</t>
-  </si>
-  <si>
-    <t>A1760</t>
-  </si>
-  <si>
-    <t>A1820</t>
-  </si>
-  <si>
-    <t>Commissioning / Controls Support</t>
-  </si>
-  <si>
-    <t>A1830</t>
-  </si>
-  <si>
-    <t>TAB Team</t>
-  </si>
-  <si>
-    <t>A1840</t>
-  </si>
-  <si>
-    <t>A1860</t>
-  </si>
-  <si>
-    <t>Total Cost</t>
-  </si>
-  <si>
-    <t>total_cost</t>
-  </si>
-  <si>
-    <t>CONSUMABLE</t>
-  </si>
-  <si>
-    <t>Backfill/Compaction (cy/hr)</t>
-  </si>
-  <si>
-    <t>backfill_compaction_cy_hr_</t>
-  </si>
-  <si>
-    <t>MEP Rough-In per Trade (sf/hr)</t>
-  </si>
-  <si>
-    <t>mep_rough_in_per_trade_sf_hr_</t>
-  </si>
-  <si>
-    <t>Hauling (cy/hr)</t>
-  </si>
-  <si>
-    <t>hauling_cy_hr_</t>
-  </si>
-  <si>
-    <t>Interior (sf/hr)</t>
-  </si>
-  <si>
-    <t>interior_sf_hr_</t>
-  </si>
-  <si>
-    <t>Excavation (cy/hr)</t>
-  </si>
-  <si>
-    <t>excavation_cy_hr_</t>
-  </si>
-  <si>
-    <t>Proofroll (sf/hr)</t>
-  </si>
-  <si>
-    <t>proofroll_sf_hr_</t>
-  </si>
-  <si>
-    <t>Slab-on-Grade (sf/hr)</t>
-  </si>
-  <si>
-    <t>slab_on_grade_sf_hr_</t>
-  </si>
-  <si>
-    <t>Install Construction Fencing</t>
-  </si>
-  <si>
-    <t>REGULAR</t>
-  </si>
-  <si>
-    <t>MANUAL</t>
-  </si>
-  <si>
-    <t>Default calendar</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>NOT_STARTED</t>
-  </si>
-  <si>
-    <t>2029-10-01T09:00</t>
-  </si>
-  <si>
-    <t>2029-10-03T17:00</t>
-  </si>
-  <si>
-    <t>cbd410b2-5548-4cd2-8527-f2345a50d57f</t>
-  </si>
-  <si>
-    <t>Install Site Office &amp; Welfare Units</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2029-10-04T09:00</t>
-  </si>
-  <si>
-    <t>2029-10-09T17:00</t>
-  </si>
-  <si>
-    <t>Temporary Water Installation</t>
-  </si>
-  <si>
-    <t>2029-10-08T17:00</t>
-  </si>
-  <si>
-    <t>Temporary Power Installation</t>
-  </si>
-  <si>
-    <t>Tree Removal &amp; Clearing</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>2029-10-10T17:00</t>
-  </si>
-  <si>
-    <t>Bleacher Demolition</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>2029-10-12T17:00</t>
-  </si>
-  <si>
-    <t>Crane Pad Construction</t>
-  </si>
-  <si>
-    <t>2029-10-11T09:00</t>
-  </si>
-  <si>
-    <t>2029-10-17T17:00</t>
-  </si>
-  <si>
-    <t>Laydown Area Preparation</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Full Basement Excavation</t>
-  </si>
-  <si>
-    <t>0d25cbc5-489e-404b-bca9-c37d58b2aab2</t>
-  </si>
-  <si>
-    <t>Shoring / Stabilization</t>
-  </si>
-  <si>
-    <t>2029-10-10T09:00</t>
-  </si>
-  <si>
-    <t>2029-10-16T17:00</t>
-  </si>
-  <si>
-    <t>Subgrade Preparation</t>
-  </si>
-  <si>
-    <t>2029-10-15T17:00</t>
-  </si>
-  <si>
-    <t>Footings – Form/Rebar/Pour</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>2029-10-16T09:00</t>
-  </si>
-  <si>
-    <t>2029-10-29T17:00</t>
-  </si>
-  <si>
-    <t>Grade Beams</t>
-  </si>
-  <si>
-    <t>2029-11-08T09:00</t>
-  </si>
-  <si>
-    <t>2029-11-16T17:00</t>
-  </si>
-  <si>
-    <t>Basement Retaining Walls</t>
-  </si>
-  <si>
-    <t>2029-11-19T09:00</t>
-  </si>
-  <si>
-    <t>2029-11-21T17:00</t>
-  </si>
-  <si>
-    <t>Waterproofing &amp; Drainage</t>
-  </si>
-  <si>
-    <t>2029-11-22T09:00</t>
-  </si>
-  <si>
-    <t>2029-11-28T17:00</t>
-  </si>
-  <si>
-    <t>Basement Slab on Grade</t>
-  </si>
-  <si>
-    <t>2029-12-17T09:00</t>
-  </si>
-  <si>
-    <t>2029-12-25T17:00</t>
-  </si>
-  <si>
-    <t>Underground Utilities</t>
-  </si>
-  <si>
-    <t>2029-11-29T09:00</t>
-  </si>
-  <si>
-    <t>2029-12-07T17:00</t>
-  </si>
-  <si>
-    <t>Backfill &amp; Compaction</t>
-  </si>
-  <si>
-    <t>2029-12-10T09:00</t>
-  </si>
-  <si>
-    <t>2029-12-14T17:00</t>
-  </si>
-  <si>
-    <t>Foundational Columns</t>
-  </si>
-  <si>
-    <t>2029-10-30T09:00</t>
-  </si>
-  <si>
-    <t>2029-11-07T17:00</t>
-  </si>
-  <si>
-    <t>Frame: Columns</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>2030-01-08T09:00</t>
-  </si>
-  <si>
-    <t>2030-01-15T17:00</t>
-  </si>
-  <si>
-    <t>877325b6-0ec2-4dc8-b9e3-cfa6b8292d16</t>
-  </si>
-  <si>
-    <t>Floor</t>
-  </si>
-  <si>
-    <t>2030-01-03T09:00</t>
-  </si>
-  <si>
-    <t>2030-01-07T17:00</t>
-  </si>
-  <si>
-    <t>A1350</t>
-  </si>
-  <si>
-    <t>Frame: Beams</t>
-  </si>
-  <si>
-    <t>2029-12-26T09:00</t>
-  </si>
-  <si>
-    <t>2030-01-02T17:00</t>
-  </si>
-  <si>
-    <t>Roof</t>
-  </si>
-  <si>
-    <t>2030-01-16T09:00</t>
-  </si>
-  <si>
-    <t>2030-01-21T17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facade Install + Glazing </t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>2030-01-22T09:00</t>
-  </si>
-  <si>
-    <t>2030-03-06T17:00</t>
-  </si>
-  <si>
-    <t>63195f08-e779-4f3a-ae3a-306d40e10c1c</t>
-  </si>
-  <si>
-    <t>Mechanical Room Buildout</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>2030-03-07T09:00</t>
-  </si>
-  <si>
-    <t>2030-03-26T17:00</t>
-  </si>
-  <si>
-    <t>c3929e98-3e87-4181-a90c-ec2646e7d440</t>
-  </si>
-  <si>
-    <t>Main Electrical &amp; Riser Install</t>
-  </si>
-  <si>
-    <t>MEP Rough-In</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>2030-03-27T09:00</t>
-  </si>
-  <si>
-    <t>2030-05-31T17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interior Framing </t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>2030-03-22T17:00</t>
-  </si>
-  <si>
-    <t>da7c403f-4319-48fd-8009-37270386cab6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drywall &amp; Finishes </t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>2030-03-25T09:00</t>
-  </si>
-  <si>
-    <t>2030-04-25T17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceiling Installation </t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>2030-04-26T09:00</t>
-  </si>
-  <si>
-    <t>2030-05-17T17:00</t>
-  </si>
-  <si>
-    <t>MEP Start-Up</t>
-  </si>
-  <si>
-    <t>2030-05-20T09:00</t>
-  </si>
-  <si>
-    <t>2030-05-28T17:00</t>
-  </si>
-  <si>
-    <t>383f728a-1104-4558-be7b-db47650d4deb</t>
-  </si>
-  <si>
-    <t>TAB</t>
-  </si>
-  <si>
-    <t>2030-05-29T09:00</t>
-  </si>
-  <si>
-    <t>2030-06-06T17:00</t>
-  </si>
-  <si>
-    <t>Integrated Systems Testing</t>
-  </si>
-  <si>
-    <t>2030-06-07T09:00</t>
-  </si>
-  <si>
-    <t>2030-06-13T17:00</t>
-  </si>
-  <si>
-    <t>Final Inspections</t>
-  </si>
-  <si>
-    <t>2030-05-24T17:00</t>
-  </si>
-  <si>
-    <t>A1880</t>
-  </si>
-  <si>
-    <t>Hurricane Contingency Buffer</t>
-  </si>
-  <si>
-    <t>2030-06-14T09:00</t>
-  </si>
-  <si>
-    <t>2030-07-03T17:00</t>
+    <t>FS</t>
   </si>
   <si>
     <t>compactor_roller</t>
@@ -840,60 +897,6 @@
   </si>
   <si>
     <t>scissor_lift</t>
-  </si>
-  <si>
-    <t>3837e7c2-0906-4333-ac9b-a2737d9ef3ab</t>
-  </si>
-  <si>
-    <t>Island 2026</t>
-  </si>
-  <si>
-    <t>project</t>
-  </si>
-  <si>
-    <t>SITE PREPARATION &amp; DEMOLITION</t>
-  </si>
-  <si>
-    <t>project.SITE PREPARATION &amp; DEMOLITION</t>
-  </si>
-  <si>
-    <t>EARTHWORK &amp; BASEMENT</t>
-  </si>
-  <si>
-    <t>project.EARTHWORK &amp; BASEMENT</t>
-  </si>
-  <si>
-    <t>SUPERSTRUCTURE</t>
-  </si>
-  <si>
-    <t>project.SUPERSTRUCTURE – ZONE A</t>
-  </si>
-  <si>
-    <t>ENVELOPE</t>
-  </si>
-  <si>
-    <t>project.ENVELOPE</t>
-  </si>
-  <si>
-    <t>MEP INSTALLATION</t>
-  </si>
-  <si>
-    <t>project.MEP INSTALLATION</t>
-  </si>
-  <si>
-    <t>INTERIOR</t>
-  </si>
-  <si>
-    <t>project.INTERIOR FINISHES</t>
-  </si>
-  <si>
-    <t>COMMISSIONING &amp; CLOSEOUT</t>
-  </si>
-  <si>
-    <t>project.COMMISSIONING &amp; CLOSEOUT</t>
-  </si>
-  <si>
-    <t>FS</t>
   </si>
   <si>
     <t>commissioning_controls_support</t>
@@ -1460,114 +1463,114 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>270</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
       <c r="C2" t="n">
         <v>1.0</v>
       </c>
       <c r="D2" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="C3" t="n">
         <v>2.0</v>
       </c>
       <c r="D3" t="s">
-        <v>274</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>141</v>
       </c>
       <c r="C4" t="n">
         <v>2.0</v>
       </c>
       <c r="D4" t="s">
-        <v>276</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>277</v>
+        <v>144</v>
       </c>
       <c r="C5" t="n">
         <v>2.0</v>
       </c>
       <c r="D5" t="s">
-        <v>278</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>279</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
         <v>2.0</v>
       </c>
       <c r="D6" t="s">
-        <v>280</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
         <v>2.0</v>
       </c>
       <c r="D7" t="s">
-        <v>282</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
         <v>2.0</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>243</v>
+        <v>155</v>
       </c>
       <c r="B9" t="s">
-        <v>285</v>
+        <v>156</v>
       </c>
       <c r="C9" t="n">
         <v>2.0</v>
       </c>
       <c r="D9" t="s">
-        <v>286</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -1607,10 +1610,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="C2" t="n">
         <v>35.0</v>
@@ -1618,10 +1621,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="C3" t="n">
         <v>200.0</v>
@@ -1629,10 +1632,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="C4" t="n">
         <v>30.0</v>
@@ -1640,10 +1643,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
         <v>250.0</v>
@@ -1651,10 +1654,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="C6" t="n">
         <v>40.0</v>
@@ -1662,10 +1665,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="C7" t="n">
         <v>2000.0</v>
@@ -1673,10 +1676,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
         <v>300.0</v>
@@ -1737,7 +1740,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:AB36"/>
+  <dimension ref="A2:AB37"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="24" max="24" customWidth="true" hidden="false" style="0" width="20.0" collapsed="false" outlineLevel="0"/>
@@ -1862,32 +1865,32 @@
         <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E2"/>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G2" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J2" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="K2" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="L2" t="n">
         <v>0.0</v>
@@ -1899,10 +1902,10 @@
       <c r="Q2"/>
       <c r="R2"/>
       <c r="S2" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="T2" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="U2" t="n">
         <v>0.0</v>
@@ -1917,7 +1920,7 @@
         <v>185.0</v>
       </c>
       <c r="Y2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Z2"/>
       <c r="AA2"/>
@@ -1928,32 +1931,32 @@
         <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G3" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J3" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="K3" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="L3" t="n">
         <v>0.0</v>
@@ -1965,10 +1968,10 @@
       <c r="Q3"/>
       <c r="R3"/>
       <c r="S3" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="T3" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="U3" t="n">
         <v>1528.0</v>
@@ -1983,7 +1986,7 @@
         <v>191.0</v>
       </c>
       <c r="Y3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Z3"/>
       <c r="AA3"/>
@@ -1994,32 +1997,32 @@
         <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G4" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J4" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="K4" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="L4" t="n">
         <v>0.0</v>
@@ -2031,10 +2034,10 @@
       <c r="Q4"/>
       <c r="R4"/>
       <c r="S4" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="T4" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="U4" t="n">
         <v>1536.0</v>
@@ -2049,7 +2052,7 @@
         <v>192.0</v>
       </c>
       <c r="Y4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Z4"/>
       <c r="AA4"/>
@@ -2060,32 +2063,32 @@
         <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E5"/>
       <c r="F5" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G5" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J5" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="K5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="L5" t="n">
         <v>0.0</v>
@@ -2097,10 +2100,10 @@
       <c r="Q5"/>
       <c r="R5"/>
       <c r="S5" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="T5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="U5" t="n">
         <v>1528.0</v>
@@ -2115,7 +2118,7 @@
         <v>191.0</v>
       </c>
       <c r="Y5" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Z5"/>
       <c r="AA5"/>
@@ -2126,32 +2129,32 @@
         <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G6" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J6" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="K6" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="L6" t="n">
         <v>0.0</v>
@@ -2163,10 +2166,10 @@
       <c r="Q6"/>
       <c r="R6"/>
       <c r="S6" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="T6" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="U6" t="n">
         <v>0.0</v>
@@ -2181,7 +2184,7 @@
         <v>185.0</v>
       </c>
       <c r="Y6" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Z6"/>
       <c r="AA6"/>
@@ -2192,32 +2195,32 @@
         <v>89</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G7" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J7" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="K7" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="L7" t="n">
         <v>0.0</v>
@@ -2229,10 +2232,10 @@
       <c r="Q7"/>
       <c r="R7"/>
       <c r="S7" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="T7" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="U7" t="n">
         <v>1504.0</v>
@@ -2247,7 +2250,7 @@
         <v>188.0</v>
       </c>
       <c r="Y7" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Z7"/>
       <c r="AA7"/>
@@ -2258,32 +2261,32 @@
         <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G8" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J8" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="K8" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="L8" t="n">
         <v>0.0</v>
@@ -2295,10 +2298,10 @@
       <c r="Q8"/>
       <c r="R8"/>
       <c r="S8" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="T8" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="U8" t="n">
         <v>1480.0</v>
@@ -2313,7 +2316,7 @@
         <v>185.0</v>
       </c>
       <c r="Y8" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Z8"/>
       <c r="AA8"/>
@@ -2324,32 +2327,32 @@
         <v>92</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E9"/>
       <c r="F9" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G9" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J9" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="K9" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="L9" t="n">
         <v>0.0</v>
@@ -2361,10 +2364,10 @@
       <c r="Q9"/>
       <c r="R9"/>
       <c r="S9" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="T9" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="U9" t="n">
         <v>1520.0</v>
@@ -2379,7 +2382,7 @@
         <v>190.0</v>
       </c>
       <c r="Y9" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Z9"/>
       <c r="AA9"/>
@@ -2387,35 +2390,35 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E10"/>
       <c r="F10" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G10" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J10" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="K10" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="L10" t="n">
         <v>0.0</v>
@@ -2427,10 +2430,10 @@
       <c r="Q10"/>
       <c r="R10"/>
       <c r="S10" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="T10" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="U10" t="n">
         <v>0.0</v>
@@ -2445,7 +2448,7 @@
         <v>0.0</v>
       </c>
       <c r="Y10" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z10"/>
       <c r="AA10"/>
@@ -2453,35 +2456,35 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="C11" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E11"/>
       <c r="F11" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G11" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J11" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="K11" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="L11" t="n">
         <v>0.0</v>
@@ -2493,10 +2496,10 @@
       <c r="Q11"/>
       <c r="R11"/>
       <c r="S11" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="T11" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="U11" t="n">
         <v>1488.0</v>
@@ -2511,7 +2514,7 @@
         <v>186.0</v>
       </c>
       <c r="Y11" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z11"/>
       <c r="AA11"/>
@@ -2519,35 +2522,35 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G12" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J12" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="K12" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="L12" t="n">
         <v>0.0</v>
@@ -2559,10 +2562,10 @@
       <c r="Q12"/>
       <c r="R12"/>
       <c r="S12" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="T12" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="U12" t="n">
         <v>0.0</v>
@@ -2577,7 +2580,7 @@
         <v>0.0</v>
       </c>
       <c r="Y12" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z12"/>
       <c r="AA12"/>
@@ -2585,35 +2588,35 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J13" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="K13" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="L13" t="n">
         <v>0.0</v>
@@ -2625,10 +2628,10 @@
       <c r="Q13"/>
       <c r="R13"/>
       <c r="S13" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="T13" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="U13" t="n">
         <v>0.0</v>
@@ -2643,7 +2646,7 @@
         <v>0.0</v>
       </c>
       <c r="Y13" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z13"/>
       <c r="AA13"/>
@@ -2651,35 +2654,35 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E14"/>
       <c r="F14" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G14" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J14" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="K14" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="L14" t="n">
         <v>0.0</v>
@@ -2691,10 +2694,10 @@
       <c r="Q14"/>
       <c r="R14"/>
       <c r="S14" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="T14" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="U14" t="n">
         <v>0.0</v>
@@ -2709,7 +2712,7 @@
         <v>0.0</v>
       </c>
       <c r="Y14" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z14"/>
       <c r="AA14"/>
@@ -2717,35 +2720,35 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G15" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J15" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="K15" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="L15" t="n">
         <v>0.0</v>
@@ -2757,10 +2760,10 @@
       <c r="Q15"/>
       <c r="R15"/>
       <c r="S15" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="T15" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="U15" t="n">
         <v>0.0</v>
@@ -2775,7 +2778,7 @@
         <v>0.0</v>
       </c>
       <c r="Y15" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z15"/>
       <c r="AA15"/>
@@ -2783,35 +2786,35 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G16" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J16" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="K16" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="L16" t="n">
         <v>0.0</v>
@@ -2823,10 +2826,10 @@
       <c r="Q16"/>
       <c r="R16"/>
       <c r="S16" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="U16" t="n">
         <v>0.0</v>
@@ -2841,7 +2844,7 @@
         <v>0.0</v>
       </c>
       <c r="Y16" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z16"/>
       <c r="AA16"/>
@@ -2849,35 +2852,35 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E17"/>
       <c r="F17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G17" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J17" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="K17" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="L17" t="n">
         <v>0.0</v>
@@ -2889,10 +2892,10 @@
       <c r="Q17"/>
       <c r="R17"/>
       <c r="S17" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="T17" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="U17" t="n">
         <v>0.0</v>
@@ -2907,7 +2910,7 @@
         <v>0.0</v>
       </c>
       <c r="Y17" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z17"/>
       <c r="AA17"/>
@@ -2915,35 +2918,35 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E18"/>
       <c r="F18" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G18" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J18" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="K18" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="L18" t="n">
         <v>0.0</v>
@@ -2955,10 +2958,10 @@
       <c r="Q18"/>
       <c r="R18"/>
       <c r="S18" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="T18" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="U18" t="n">
         <v>0.0</v>
@@ -2973,7 +2976,7 @@
         <v>0.0</v>
       </c>
       <c r="Y18" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z18"/>
       <c r="AA18"/>
@@ -2981,35 +2984,35 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B19" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G19" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J19" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="K19" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="L19" t="n">
         <v>0.0</v>
@@ -3021,10 +3024,10 @@
       <c r="Q19"/>
       <c r="R19"/>
       <c r="S19" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="T19" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="U19" t="n">
         <v>0.0</v>
@@ -3039,7 +3042,7 @@
         <v>0.0</v>
       </c>
       <c r="Y19" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z19"/>
       <c r="AA19"/>
@@ -3047,35 +3050,35 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E20"/>
       <c r="F20" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G20" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J20" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="K20" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="L20" t="n">
         <v>0.0</v>
@@ -3087,10 +3090,10 @@
       <c r="Q20"/>
       <c r="R20"/>
       <c r="S20" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="T20" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="U20" t="n">
         <v>0.0</v>
@@ -3105,7 +3108,7 @@
         <v>0.0</v>
       </c>
       <c r="Y20" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="Z20"/>
       <c r="AA20"/>
@@ -3113,35 +3116,35 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E21"/>
       <c r="F21" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G21" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J21" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="K21" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="L21" t="n">
         <v>0.0</v>
@@ -3153,10 +3156,10 @@
       <c r="Q21"/>
       <c r="R21"/>
       <c r="S21" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="T21" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="U21" t="n">
         <v>0.0</v>
@@ -3171,7 +3174,7 @@
         <v>0.0</v>
       </c>
       <c r="Y21" t="s">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="Z21"/>
       <c r="AA21"/>
@@ -3179,35 +3182,35 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="C22" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E22"/>
       <c r="F22" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G22" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J22" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="K22" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="L22" t="n">
         <v>0.0</v>
@@ -3219,10 +3222,10 @@
       <c r="Q22"/>
       <c r="R22"/>
       <c r="S22" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="T22" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="U22" t="n">
         <v>0.0</v>
@@ -3237,7 +3240,7 @@
         <v>0.0</v>
       </c>
       <c r="Y22" t="s">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="Z22"/>
       <c r="AA22"/>
@@ -3245,35 +3248,35 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E23"/>
       <c r="F23" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G23" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J23" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="K23" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="L23" t="n">
         <v>0.0</v>
@@ -3285,10 +3288,10 @@
       <c r="Q23"/>
       <c r="R23"/>
       <c r="S23" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="T23" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="U23" t="n">
         <v>0.0</v>
@@ -3303,7 +3306,7 @@
         <v>0.0</v>
       </c>
       <c r="Y23" t="s">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="Z23"/>
       <c r="AA23"/>
@@ -3311,35 +3314,35 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E24"/>
       <c r="F24" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G24" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J24" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="K24" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="L24" t="n">
         <v>0.0</v>
@@ -3351,10 +3354,10 @@
       <c r="Q24"/>
       <c r="R24"/>
       <c r="S24" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="T24" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="U24" t="n">
         <v>0.0</v>
@@ -3369,7 +3372,7 @@
         <v>0.0</v>
       </c>
       <c r="Y24" t="s">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="Z24"/>
       <c r="AA24"/>
@@ -3377,35 +3380,35 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="C25" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E25"/>
       <c r="F25" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G25" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J25" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="K25" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="L25" t="n">
         <v>0.0</v>
@@ -3417,10 +3420,10 @@
       <c r="Q25"/>
       <c r="R25"/>
       <c r="S25" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="T25" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="U25" t="n">
         <v>0.0</v>
@@ -3435,7 +3438,7 @@
         <v>0.0</v>
       </c>
       <c r="Y25" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="Z25"/>
       <c r="AA25"/>
@@ -3443,35 +3446,35 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="C26" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E26"/>
       <c r="F26" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G26" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J26" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="K26" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="L26" t="n">
         <v>0.0</v>
@@ -3483,25 +3486,25 @@
       <c r="Q26"/>
       <c r="R26"/>
       <c r="S26" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="T26" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="U26" t="n">
-        <v>568.0</v>
+        <v>0.0</v>
       </c>
       <c r="V26" t="n">
-        <v>71.0</v>
+        <v>0.0</v>
       </c>
       <c r="W26" t="n">
-        <v>568.0</v>
+        <v>0.0</v>
       </c>
       <c r="X26" t="n">
-        <v>71.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y26" t="s">
-        <v>222</v>
+        <v>146</v>
       </c>
       <c r="Z26"/>
       <c r="AA26"/>
@@ -3509,35 +3512,35 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E27"/>
       <c r="F27" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G27" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J27" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="K27" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="L27" t="n">
         <v>0.0</v>
@@ -3549,25 +3552,25 @@
       <c r="Q27"/>
       <c r="R27"/>
       <c r="S27" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="T27" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0</v>
+        <v>552.0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.0</v>
+        <v>69.0</v>
       </c>
       <c r="W27" t="n">
-        <v>184.0</v>
+        <v>552.0</v>
       </c>
       <c r="X27" t="n">
-        <v>23.0</v>
+        <v>69.0</v>
       </c>
       <c r="Y27" t="s">
-        <v>222</v>
+        <v>146</v>
       </c>
       <c r="Z27"/>
       <c r="AA27"/>
@@ -3575,35 +3578,35 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B28" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="C28" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E28"/>
       <c r="F28" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G28" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J28" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="K28" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="L28" t="n">
         <v>0.0</v>
@@ -3615,25 +3618,25 @@
       <c r="Q28"/>
       <c r="R28"/>
       <c r="S28" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="T28" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="U28" t="n">
-        <v>184.0</v>
+        <v>568.0</v>
       </c>
       <c r="V28" t="n">
-        <v>23.0</v>
+        <v>71.0</v>
       </c>
       <c r="W28" t="n">
-        <v>184.0</v>
+        <v>568.0</v>
       </c>
       <c r="X28" t="n">
-        <v>23.0</v>
+        <v>71.0</v>
       </c>
       <c r="Y28" t="s">
-        <v>222</v>
+        <v>149</v>
       </c>
       <c r="Z28"/>
       <c r="AA28"/>
@@ -3641,35 +3644,35 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B29" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E29"/>
       <c r="F29" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G29" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J29" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="K29" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="L29" t="n">
         <v>0.0</v>
@@ -3681,10 +3684,10 @@
       <c r="Q29"/>
       <c r="R29"/>
       <c r="S29" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="T29" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="U29" t="n">
         <v>0.0</v>
@@ -3693,13 +3696,13 @@
         <v>0.0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.0</v>
+        <v>184.0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="Y29" t="s">
-        <v>231</v>
+        <v>149</v>
       </c>
       <c r="Z29"/>
       <c r="AA29"/>
@@ -3707,35 +3710,35 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B30" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E30"/>
       <c r="F30" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G30" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J30" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="K30" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L30" t="n">
         <v>0.0</v>
@@ -3747,25 +3750,25 @@
       <c r="Q30"/>
       <c r="R30"/>
       <c r="S30" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="T30" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0</v>
+        <v>184.0</v>
       </c>
       <c r="V30" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0</v>
+        <v>184.0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
       <c r="Y30" t="s">
-        <v>231</v>
+        <v>149</v>
       </c>
       <c r="Z30"/>
       <c r="AA30"/>
@@ -3773,35 +3776,35 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B31" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E31"/>
       <c r="F31" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G31" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J31" t="s">
         <v>238</v>
       </c>
       <c r="K31" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="L31" t="n">
         <v>0.0</v>
@@ -3816,7 +3819,7 @@
         <v>238</v>
       </c>
       <c r="T31" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="U31" t="n">
         <v>0.0</v>
@@ -3831,7 +3834,7 @@
         <v>0.0</v>
       </c>
       <c r="Y31" t="s">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="Z31"/>
       <c r="AA31"/>
@@ -3839,35 +3842,35 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B32" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C32" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E32"/>
       <c r="F32" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G32" t="s">
-        <v>159</v>
+        <v>230</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J32" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="K32" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="L32" t="n">
         <v>0.0</v>
@@ -3879,10 +3882,10 @@
       <c r="Q32"/>
       <c r="R32"/>
       <c r="S32" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="T32" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="U32" t="n">
         <v>0.0</v>
@@ -3897,7 +3900,7 @@
         <v>0.0</v>
       </c>
       <c r="Y32" t="s">
-        <v>243</v>
+        <v>152</v>
       </c>
       <c r="Z32"/>
       <c r="AA32"/>
@@ -3905,35 +3908,35 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B33" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E33"/>
       <c r="F33" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G33" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J33" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="K33" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="L33" t="n">
         <v>0.0</v>
@@ -3945,10 +3948,10 @@
       <c r="Q33"/>
       <c r="R33"/>
       <c r="S33" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="T33" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="U33" t="n">
         <v>0.0</v>
@@ -3963,7 +3966,7 @@
         <v>0.0</v>
       </c>
       <c r="Y33" t="s">
-        <v>243</v>
+        <v>155</v>
       </c>
       <c r="Z33"/>
       <c r="AA33"/>
@@ -3971,35 +3974,35 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D34" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E34"/>
       <c r="F34" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G34" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J34" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="K34" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="L34" t="n">
         <v>0.0</v>
@@ -4011,10 +4014,10 @@
       <c r="Q34"/>
       <c r="R34"/>
       <c r="S34" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="T34" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U34" t="n">
         <v>0.0</v>
@@ -4029,7 +4032,7 @@
         <v>0.0</v>
       </c>
       <c r="Y34" t="s">
-        <v>243</v>
+        <v>155</v>
       </c>
       <c r="Z34"/>
       <c r="AA34"/>
@@ -4037,35 +4040,35 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C35" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D35" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E35"/>
       <c r="F35" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G35" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J35" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="K35" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="L35" t="n">
         <v>0.0</v>
@@ -4077,25 +4080,25 @@
       <c r="Q35"/>
       <c r="R35"/>
       <c r="S35" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="T35" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="U35" t="n">
-        <v>224.0</v>
+        <v>0.0</v>
       </c>
       <c r="V35" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="W35" t="n">
-        <v>224.0</v>
+        <v>0.0</v>
       </c>
       <c r="X35" t="n">
-        <v>28.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y35" t="s">
-        <v>243</v>
+        <v>155</v>
       </c>
       <c r="Z35"/>
       <c r="AA35"/>
@@ -4103,35 +4106,35 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>252</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D36" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E36"/>
       <c r="F36" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G36" t="s">
-        <v>219</v>
+        <v>174</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K36" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="L36" t="n">
         <v>0.0</v>
@@ -4143,29 +4146,95 @@
       <c r="Q36"/>
       <c r="R36"/>
       <c r="S36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="T36" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="U36" t="n">
-        <v>0.0</v>
+        <v>224.0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.0</v>
+        <v>224.0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="Y36" t="s">
-        <v>243</v>
+        <v>155</v>
       </c>
       <c r="Z36"/>
       <c r="AA36"/>
       <c r="AB36"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>265</v>
+      </c>
+      <c r="B37" t="s">
+        <v>266</v>
+      </c>
+      <c r="C37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37"/>
+      <c r="F37" t="s">
+        <v>161</v>
+      </c>
+      <c r="G37" t="s">
+        <v>241</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="s">
+        <v>163</v>
+      </c>
+      <c r="J37" t="s">
+        <v>267</v>
+      </c>
+      <c r="K37" t="s">
+        <v>268</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+      <c r="S37" t="s">
+        <v>267</v>
+      </c>
+      <c r="T37" t="s">
+        <v>268</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z37"/>
+      <c r="AA37"/>
+      <c r="AB37"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4183,7 +4252,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:D36"/>
+  <dimension ref="A2:D37"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" hidden="false" style="0" width="20.0" collapsed="false" outlineLevel="0"/>
@@ -4214,7 +4283,7 @@
         <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D2" t="n">
         <v>0.0</v>
@@ -4228,7 +4297,7 @@
         <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D3" t="n">
         <v>0.0</v>
@@ -4242,7 +4311,7 @@
         <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D4" t="n">
         <v>0.0</v>
@@ -4256,7 +4325,7 @@
         <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D5" t="n">
         <v>0.0</v>
@@ -4270,7 +4339,7 @@
         <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D6" t="n">
         <v>0.0</v>
@@ -4284,7 +4353,7 @@
         <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D7" t="n">
         <v>0.0</v>
@@ -4298,7 +4367,7 @@
         <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
         <v>0.0</v>
@@ -4306,13 +4375,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
         <v>0.0</v>
@@ -4320,13 +4389,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
         <v>0.0</v>
@@ -4334,13 +4403,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D11" t="n">
         <v>0.0</v>
@@ -4348,13 +4417,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D12" t="n">
         <v>0.0</v>
@@ -4362,13 +4431,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D13" t="n">
         <v>0.0</v>
@@ -4376,13 +4445,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D14" t="n">
         <v>0.0</v>
@@ -4390,13 +4459,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D15" t="n">
         <v>0.0</v>
@@ -4404,13 +4473,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C16" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D16" t="n">
         <v>0.0</v>
@@ -4418,13 +4487,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D17" t="n">
         <v>0.0</v>
@@ -4432,13 +4501,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D18" t="n">
         <v>0.0</v>
@@ -4446,13 +4515,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D19" t="n">
         <v>0.0</v>
@@ -4460,13 +4529,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D20" t="n">
         <v>0.0</v>
@@ -4474,13 +4543,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D21" t="n">
         <v>0.0</v>
@@ -4488,13 +4557,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D22" t="n">
         <v>0.0</v>
@@ -4502,13 +4571,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D23" t="n">
         <v>0.0</v>
@@ -4516,13 +4585,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>233</v>
       </c>
       <c r="C24" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D24" t="n">
         <v>0.0</v>
@@ -4530,13 +4599,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D25" t="n">
         <v>0.0</v>
@@ -4544,13 +4613,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D26" t="n">
         <v>0.0</v>
@@ -4558,13 +4627,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D27" t="n">
         <v>0.0</v>
@@ -4572,13 +4641,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D28" t="n">
         <v>0.0</v>
@@ -4586,13 +4655,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D29" t="n">
         <v>0.0</v>
@@ -4600,13 +4669,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D30" t="n">
         <v>0.0</v>
@@ -4614,13 +4683,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D31" t="n">
         <v>0.0</v>
@@ -4628,13 +4697,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D32" t="n">
         <v>0.0</v>
@@ -4642,13 +4711,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D33" t="n">
         <v>0.0</v>
@@ -4656,13 +4725,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D34" t="n">
         <v>0.0</v>
@@ -4670,13 +4739,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D35" t="n">
         <v>0.0</v>
@@ -4684,15 +4753,29 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s">
-        <v>252</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D36" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" t="s">
+        <v>265</v>
+      </c>
+      <c r="C37" t="s">
+        <v>274</v>
+      </c>
+      <c r="D37" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -4773,10 +4856,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C2" t="n">
         <v>1.0</v>
@@ -4794,7 +4877,7 @@
         <v>300.0</v>
       </c>
       <c r="H2" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -4805,15 +4888,15 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C3" t="n">
         <v>1.0</v>
@@ -4831,7 +4914,7 @@
         <v>240.0</v>
       </c>
       <c r="H3" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -4845,10 +4928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C4" t="n">
         <v>1.0</v>
@@ -4866,7 +4949,7 @@
         <v>520.0</v>
       </c>
       <c r="H4" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -4877,15 +4960,15 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C5" t="n">
         <v>1.0</v>
@@ -4903,7 +4986,7 @@
         <v>490.0</v>
       </c>
       <c r="H5" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -4914,15 +4997,15 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
         <v>1.0</v>
@@ -4940,7 +5023,7 @@
         <v>560.0</v>
       </c>
       <c r="H6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4951,15 +5034,15 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C7" t="n">
         <v>1.0</v>
@@ -4977,7 +5060,7 @@
         <v>350.0</v>
       </c>
       <c r="H7" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4988,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8">
@@ -4996,7 +5079,7 @@
         <v>90</v>
       </c>
       <c r="B8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C8" t="n">
         <v>1.0</v>
@@ -5014,7 +5097,7 @@
         <v>320.0</v>
       </c>
       <c r="H8" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5025,15 +5108,15 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C9" t="n">
         <v>2.0</v>
@@ -5051,7 +5134,7 @@
         <v>0.0</v>
       </c>
       <c r="H9" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -5062,15 +5145,15 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C10" t="n">
         <v>2.0</v>
@@ -5088,7 +5171,7 @@
         <v>0.0</v>
       </c>
       <c r="H10" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -5099,15 +5182,15 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C11" t="n">
         <v>1.0</v>
@@ -5125,7 +5208,7 @@
         <v>360.0</v>
       </c>
       <c r="H11" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -5136,15 +5219,15 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C12" t="n">
         <v>1.0</v>
@@ -5162,7 +5245,7 @@
         <v>480.0</v>
       </c>
       <c r="H12" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -5173,15 +5256,15 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C13" t="n">
         <v>1.0</v>
@@ -5199,7 +5282,7 @@
         <v>300.0</v>
       </c>
       <c r="H13" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -5210,15 +5293,15 @@
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C14" t="n">
         <v>1.0</v>
@@ -5236,7 +5319,7 @@
         <v>450.0</v>
       </c>
       <c r="H14" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -5247,15 +5330,15 @@
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C15" t="n">
         <v>1.0</v>
@@ -5273,7 +5356,7 @@
         <v>450.0</v>
       </c>
       <c r="H15" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -5284,15 +5367,15 @@
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B16" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C16" t="n">
         <v>1.0</v>
@@ -5310,7 +5393,7 @@
         <v>450.0</v>
       </c>
       <c r="H16" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -5321,15 +5404,15 @@
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C17" t="n">
         <v>1.0</v>
@@ -5347,7 +5430,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -5358,15 +5441,15 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B18" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C18" t="n">
         <v>1.0</v>
@@ -5384,7 +5467,7 @@
         <v>330.0</v>
       </c>
       <c r="H18" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -5398,10 +5481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C19" t="n">
         <v>1.0</v>
@@ -5419,7 +5502,7 @@
         <v>260.0</v>
       </c>
       <c r="H19" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -5430,15 +5513,15 @@
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C20" t="n">
         <v>1.0</v>
@@ -5456,7 +5539,7 @@
         <v>450.0</v>
       </c>
       <c r="H20" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -5467,15 +5550,15 @@
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B21" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C21" t="n">
         <v>1.0</v>
@@ -5493,7 +5576,7 @@
         <v>360.0</v>
       </c>
       <c r="H21" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -5507,10 +5590,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B22" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C22" t="n">
         <v>2.0</v>
@@ -5528,7 +5611,7 @@
         <v>360.0</v>
       </c>
       <c r="H22" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -5539,15 +5622,15 @@
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B23" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C23" t="n">
         <v>1.0</v>
@@ -5565,7 +5648,7 @@
         <v>260.0</v>
       </c>
       <c r="H23" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -5576,15 +5659,15 @@
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B24" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C24" t="n">
         <v>1.0</v>
@@ -5602,7 +5685,7 @@
         <v>600.0</v>
       </c>
       <c r="H24" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -5616,10 +5699,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="C25" t="n">
         <v>1.0</v>
@@ -5637,7 +5720,7 @@
         <v>250.0</v>
       </c>
       <c r="H25" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
@@ -5648,15 +5731,15 @@
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B26" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C26" t="n">
         <v>1.0</v>
@@ -5674,7 +5757,7 @@
         <v>450.0</v>
       </c>
       <c r="H26" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -5685,15 +5768,15 @@
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B27" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C27" t="n">
         <v>1.0</v>
@@ -5711,7 +5794,7 @@
         <v>560.0</v>
       </c>
       <c r="H27" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -5722,15 +5805,15 @@
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B28" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C28"/>
       <c r="D28" t="n">
@@ -5746,7 +5829,7 @@
         <v>2.0</v>
       </c>
       <c r="H28" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
@@ -5757,15 +5840,15 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B29" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C29" t="n">
         <v>1.0</v>
@@ -5783,7 +5866,7 @@
         <v>390.0</v>
       </c>
       <c r="H29" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -5794,15 +5877,15 @@
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C30" t="n">
         <v>1.0</v>
@@ -5820,7 +5903,7 @@
         <v>360.0</v>
       </c>
       <c r="H30" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -5831,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31">
@@ -5839,7 +5922,7 @@
         <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C31" t="n">
         <v>1.0</v>
@@ -5857,7 +5940,7 @@
         <v>240.0</v>
       </c>
       <c r="H31" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -5868,15 +5951,15 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C32" t="n">
         <v>1.0</v>
@@ -5894,7 +5977,7 @@
         <v>420.0</v>
       </c>
       <c r="H32" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -5908,10 +5991,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B33" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C33" t="n">
         <v>1.0</v>
@@ -5929,7 +6012,7 @@
         <v>420.0</v>
       </c>
       <c r="H33" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -5943,10 +6026,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C34" t="n">
         <v>1.0</v>
@@ -5964,7 +6047,7 @@
         <v>420.0</v>
       </c>
       <c r="H34" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -5975,15 +6058,15 @@
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C35" t="n">
         <v>1.0</v>
@@ -6001,7 +6084,7 @@
         <v>300.0</v>
       </c>
       <c r="H35" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -6012,15 +6095,15 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B36" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C36" t="n">
         <v>1.0</v>
@@ -6038,7 +6121,7 @@
         <v>180.0</v>
       </c>
       <c r="H36" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -6049,15 +6132,15 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C37" t="n">
         <v>1.0</v>
@@ -6075,7 +6158,7 @@
         <v>170.0</v>
       </c>
       <c r="H37" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -6086,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="38">
@@ -6094,7 +6177,7 @@
         <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C38" t="n">
         <v>1.0</v>
@@ -6112,7 +6195,7 @@
         <v>240.0</v>
       </c>
       <c r="H38" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -6123,15 +6206,15 @@
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B39" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C39" t="n">
         <v>1.0</v>
@@ -6149,7 +6232,7 @@
         <v>320.0</v>
       </c>
       <c r="H39" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -6160,15 +6243,15 @@
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C40" t="n">
         <v>1.0</v>
@@ -6186,7 +6269,7 @@
         <v>280.0</v>
       </c>
       <c r="H40" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6197,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -6385,10 +6468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -6401,10 +6484,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
@@ -6417,10 +6500,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
@@ -6433,10 +6516,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -6449,10 +6532,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C14" t="b">
         <v>1</v>
@@ -6465,10 +6548,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C15" t="b">
         <v>1</v>
@@ -6481,10 +6564,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
@@ -6497,10 +6580,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
         <v>99</v>
-      </c>
-      <c r="B17" t="s">
-        <v>96</v>
       </c>
       <c r="C17" t="b">
         <v>1</v>
@@ -6513,10 +6596,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C18" t="b">
         <v>1</v>
@@ -6529,10 +6612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" t="b">
         <v>0</v>
@@ -6545,10 +6628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C20" t="b">
         <v>0</v>
@@ -6561,10 +6644,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C21" t="b">
         <v>0</v>
@@ -6577,10 +6660,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C22" t="b">
         <v>0</v>
@@ -6593,10 +6676,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
@@ -6609,10 +6692,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C24" t="b">
         <v>0</v>
@@ -6625,10 +6708,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C25" t="b">
         <v>0</v>
@@ -6641,13 +6724,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>1.0</v>
@@ -6657,10 +6740,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C27" t="b">
         <v>1</v>
@@ -6673,13 +6756,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>1.0</v>
@@ -6689,13 +6772,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>1.0</v>
@@ -6705,13 +6788,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>1.0</v>
@@ -6721,10 +6804,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C31" t="b">
         <v>0</v>
@@ -6737,10 +6820,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
@@ -6753,10 +6836,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C33" t="b">
         <v>1</v>
@@ -6769,10 +6852,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C34" t="b">
         <v>1</v>
@@ -6785,10 +6868,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
@@ -6801,10 +6884,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C36" t="b">
         <v>0</v>
@@ -6817,10 +6900,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C37" t="b">
         <v>0</v>
@@ -6833,10 +6916,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C38" t="b">
         <v>1</v>
@@ -6849,10 +6932,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C39" t="b">
         <v>1</v>
@@ -6865,10 +6948,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C40" t="b">
         <v>0</v>
@@ -6881,10 +6964,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C41" t="b">
         <v>0</v>
@@ -6897,10 +6980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
@@ -6913,10 +6996,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C43" t="b">
         <v>1</v>
@@ -6980,13 +7063,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D2" t="n">
         <v>999999.0</v>
@@ -7101,10 +7184,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>271</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="C2" t="n">
         <v>1.0</v>
@@ -7118,7 +7201,7 @@
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -7127,10 +7210,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="C3" t="n">
         <v>1.0</v>
@@ -7144,7 +7227,7 @@
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -7153,10 +7236,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="B4" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="C4" t="n">
         <v>1.0</v>
@@ -7170,7 +7253,7 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -7179,10 +7262,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="C5" t="n">
         <v>4.0</v>
@@ -7196,7 +7279,7 @@
       <c r="F5"/>
       <c r="G5"/>
       <c r="H5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -7205,10 +7288,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="B6" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="C6" t="n">
         <v>2.0</v>
@@ -7222,7 +7305,7 @@
       <c r="F6"/>
       <c r="G6"/>
       <c r="H6" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -7231,10 +7314,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="B7" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
         <v>2.0</v>
@@ -7248,7 +7331,7 @@
       <c r="F7"/>
       <c r="G7"/>
       <c r="H7" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -7257,10 +7340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="B8" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="C8" t="n">
         <v>1.0</v>
@@ -7276,21 +7359,21 @@
         <v>0.0</v>
       </c>
       <c r="H8" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="B9" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="C9" t="n">
         <v>4.0</v>
@@ -7304,7 +7387,7 @@
       <c r="F9"/>
       <c r="G9"/>
       <c r="H9" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -7348,101 +7431,101 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>271</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>271</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
